--- a/excel/levelTable.xlsx
+++ b/excel/levelTable.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>升级攻击力倍率</t>
+  </si>
+  <si>
+    <t>升级最小时间倍率</t>
+  </si>
+  <si>
+    <t>升级最大时间倍率</t>
   </si>
   <si>
     <t>人机难度选择</t>
@@ -98,6 +104,12 @@
   </si>
   <si>
     <t>attackMultiplier</t>
+  </si>
+  <si>
+    <t>timeMinMultiplier</t>
+  </si>
+  <si>
+    <t>timeMaxMultiplier</t>
   </si>
   <si>
     <t>AIdifficulty</t>
@@ -192,7 +204,6 @@
       <b/>
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -347,7 +358,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,12 +368,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,7 +737,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -756,16 +761,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -774,85 +779,85 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -895,10 +900,10 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1227,7 +1232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K612"/>
+  <dimension ref="A1:M612"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="25.125" style="1" customWidth="1"/>
@@ -1237,11 +1242,13 @@
     <col min="8" max="8" width="21.4083333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.95" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.8666666666667" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="22.8166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="20.8666666666667" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:11">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1272,156 +1279,186 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:11">
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:11">
+        <v>22</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:11">
+        <v>27</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:13">
       <c r="A4" s="13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:11">
+        <v>28</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:13">
       <c r="A5" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>29</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="15">
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6" s="15">
         <v>13</v>
@@ -1447,16 +1484,22 @@
       <c r="J6" s="15">
         <v>1.5</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L6" s="15">
+        <v>3</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="15">
         <v>2</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" s="15">
         <v>13</v>
@@ -1482,16 +1525,22 @@
       <c r="J7" s="15">
         <v>1.5</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L7" s="15">
+        <v>3</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="15">
         <v>3</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8" s="15">
         <v>13</v>
@@ -1517,16 +1566,22 @@
       <c r="J8" s="15">
         <v>1.5</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L8" s="15">
+        <v>3</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="15">
         <v>4</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" s="15">
         <v>13</v>
@@ -1552,16 +1607,22 @@
       <c r="J9" s="15">
         <v>1.5</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L9" s="15">
+        <v>3</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="15">
         <v>5</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C10" s="15">
         <v>13</v>
@@ -1587,16 +1648,22 @@
       <c r="J10" s="15">
         <v>1.5</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L10" s="15">
+        <v>3</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="15">
         <v>6</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" s="15">
         <v>13</v>
@@ -1622,16 +1689,22 @@
       <c r="J11" s="15">
         <v>1.5</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L11" s="15">
+        <v>3</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="15">
         <v>7</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C12" s="15">
         <v>13</v>
@@ -1657,16 +1730,22 @@
       <c r="J12" s="15">
         <v>1.5</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L12" s="15">
+        <v>3</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="15">
         <v>8</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C13" s="15">
         <v>13</v>
@@ -1692,16 +1771,22 @@
       <c r="J13" s="15">
         <v>1.5</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L13" s="15">
+        <v>3</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="15">
         <v>9</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C14" s="15">
         <v>13</v>
@@ -1727,16 +1812,22 @@
       <c r="J14" s="15">
         <v>1.5</v>
       </c>
-      <c r="K14" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L14" s="15">
+        <v>3</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="15">
         <v>10</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C15" s="15">
         <v>13</v>
@@ -1760,11 +1851,17 @@
       <c r="J15" s="15">
         <v>1.5</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="L15" s="15">
+        <v>3</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>

--- a/excel/levelTable.xlsx
+++ b/excel/levelTable.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>修罗</t>
-  </si>
-  <si>
-    <t>[3,4]</t>
   </si>
   <si>
     <t>神境</t>
@@ -173,14 +170,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,184 +693,184 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -1364,6 +1354,7 @@
         <v>30</v>
       </c>
       <c r="H4" s="1">
+        <f>G4+10</f>
         <v>40</v>
       </c>
       <c r="I4" s="1">
@@ -1396,16 +1387,18 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>210</v>
+        <f>E4+10</f>
+        <v>230</v>
       </c>
       <c r="F5" s="1">
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1">
-        <v>40</v>
+        <f t="shared" ref="H5:H13" si="0">G5+10</f>
+        <v>39</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
@@ -1437,16 +1430,18 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>220</v>
+        <f t="shared" ref="E6:E13" si="1">E5+10</f>
+        <v>240</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -1478,16 +1473,18 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>230</v>
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>37</v>
       </c>
       <c r="I7" s="1">
         <v>2</v>
@@ -1519,16 +1516,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>240</v>
+        <f t="shared" si="1"/>
+        <v>260</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -1560,16 +1559,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1">
-        <v>250</v>
+        <f t="shared" si="1"/>
+        <v>270</v>
       </c>
       <c r="F9" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -1601,16 +1602,18 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>260</v>
+        <f t="shared" si="1"/>
+        <v>280</v>
       </c>
       <c r="F10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1">
-        <v>37</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="I10" s="1">
         <v>2</v>
@@ -1642,16 +1645,18 @@
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>270</v>
+        <f t="shared" si="1"/>
+        <v>290</v>
       </c>
       <c r="F11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1">
-        <v>37</v>
+        <f t="shared" si="0"/>
+        <v>33</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -1683,16 +1688,18 @@
         <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>280</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="F12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H12" s="1">
-        <v>36</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="I12" s="1">
         <v>2</v>
@@ -1707,7 +1714,7 @@
         <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1715,22 +1722,24 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>290</v>
+        <f t="shared" si="1"/>
+        <v>310</v>
       </c>
       <c r="F13" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H13" s="1">
-        <v>36</v>
+        <f t="shared" si="0"/>
+        <v>31</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
@@ -1745,7 +1754,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14"/>

--- a/excel/levelTable.xlsx
+++ b/excel/levelTable.xlsx
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E5" s="1">
         <f>E4+10</f>
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="F5" s="1">
         <v>4</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ref="E6:E13" si="1">E5+10</f>
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="F11" s="1">
         <v>8</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="F12" s="1">
         <v>9</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="F13" s="1">
         <v>9</v>

--- a/excel/levelTable.xlsx
+++ b/excel/levelTable.xlsx
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E5" s="1">
         <f>E4+10</f>
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F5" s="1">
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" ref="H5:H13" si="0">G5+10</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ref="E6:E13" si="1">E5+10</f>
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1">
         <v>2</v>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -1560,17 +1560,17 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1">
         <v>2</v>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F11" s="1">
         <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -1689,17 +1689,17 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="F12" s="1">
         <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I12" s="1">
         <v>2</v>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F13" s="1">
         <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
